--- a/data/make_iaf.xlsx
+++ b/data/make_iaf.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2666"/>
+  <dimension ref="A1:C2665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40366,26 +40366,26 @@
     </row>
     <row r="2660">
       <c r="A2660" t="n">
-        <v>86136</v>
+        <v>90668</v>
       </c>
       <c r="B2660" t="inlineStr">
         <is>
-          <t>QDB BAT SEMIMATE POP ROS/SUPREMO 3,6g</t>
+          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 270Q, 30g</t>
         </is>
       </c>
       <c r="C2660" t="inlineStr">
         <is>
-          <t>Quem Disse Berenice</t>
+          <t>oBoticário</t>
         </is>
       </c>
     </row>
     <row r="2661">
       <c r="A2661" t="n">
-        <v>90668</v>
+        <v>90711</v>
       </c>
       <c r="B2661" t="inlineStr">
         <is>
-          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 270Q, 30g</t>
+          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 225N, 30g</t>
         </is>
       </c>
       <c r="C2661" t="inlineStr">
@@ -40396,11 +40396,11 @@
     </row>
     <row r="2662">
       <c r="A2662" t="n">
-        <v>90711</v>
+        <v>90716</v>
       </c>
       <c r="B2662" t="inlineStr">
         <is>
-          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 225N, 30g</t>
+          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 200N, 30g</t>
         </is>
       </c>
       <c r="C2662" t="inlineStr">
@@ -40411,11 +40411,11 @@
     </row>
     <row r="2663">
       <c r="A2663" t="n">
-        <v>90716</v>
+        <v>90719</v>
       </c>
       <c r="B2663" t="inlineStr">
         <is>
-          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 200N, 30g</t>
+          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 180Q, 30g</t>
         </is>
       </c>
       <c r="C2663" t="inlineStr">
@@ -40426,11 +40426,11 @@
     </row>
     <row r="2664">
       <c r="A2664" t="n">
-        <v>90719</v>
+        <v>87819</v>
       </c>
       <c r="B2664" t="inlineStr">
         <is>
-          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 180Q, 30g</t>
+          <t>MAKE B BATOM EASY MATE TRUE PLUM, 3,9g</t>
         </is>
       </c>
       <c r="C2664" t="inlineStr">
@@ -40441,29 +40441,14 @@
     </row>
     <row r="2665">
       <c r="A2665" t="n">
-        <v>87819</v>
+        <v>88819</v>
       </c>
       <c r="B2665" t="inlineStr">
         <is>
-          <t>MAKE B BATOM EASY MATE TRUE PLUM, 3,9g</t>
+          <t>QDB GLOSS SONHOS AVELI 4ml</t>
         </is>
       </c>
       <c r="C2665" t="inlineStr">
-        <is>
-          <t>oBoticário</t>
-        </is>
-      </c>
-    </row>
-    <row r="2666">
-      <c r="A2666" t="n">
-        <v>88819</v>
-      </c>
-      <c r="B2666" t="inlineStr">
-        <is>
-          <t>QDB GLOSS SONHOS AVELI 4ml</t>
-        </is>
-      </c>
-      <c r="C2666" t="inlineStr">
         <is>
           <t>Quem Disse Berenice</t>
         </is>

--- a/data/make_iaf.xlsx
+++ b/data/make_iaf.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2665"/>
+  <dimension ref="A1:C2661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40156,26 +40156,26 @@
     </row>
     <row r="2646">
       <c r="A2646" t="n">
-        <v>93493</v>
+        <v>90667</v>
       </c>
       <c r="B2646" t="inlineStr">
         <is>
-          <t>EUD ESPONJA MAQ FAC NIINA SECRETS PU</t>
+          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 275N, 30g</t>
         </is>
       </c>
       <c r="C2646" t="inlineStr">
         <is>
-          <t>Eudora</t>
+          <t>oBoticário</t>
         </is>
       </c>
     </row>
     <row r="2647">
       <c r="A2647" t="n">
-        <v>90667</v>
+        <v>90709</v>
       </c>
       <c r="B2647" t="inlineStr">
         <is>
-          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 275N, 30g</t>
+          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 235N, 30g</t>
         </is>
       </c>
       <c r="C2647" t="inlineStr">
@@ -40186,11 +40186,11 @@
     </row>
     <row r="2648">
       <c r="A2648" t="n">
-        <v>90709</v>
+        <v>90712</v>
       </c>
       <c r="B2648" t="inlineStr">
         <is>
-          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 235N, 30g</t>
+          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 220Q, 30g</t>
         </is>
       </c>
       <c r="C2648" t="inlineStr">
@@ -40201,11 +40201,11 @@
     </row>
     <row r="2649">
       <c r="A2649" t="n">
-        <v>90712</v>
+        <v>90720</v>
       </c>
       <c r="B2649" t="inlineStr">
         <is>
-          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 220Q, 30g</t>
+          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 175N, 30g</t>
         </is>
       </c>
       <c r="C2649" t="inlineStr">
@@ -40216,11 +40216,11 @@
     </row>
     <row r="2650">
       <c r="A2650" t="n">
-        <v>90720</v>
+        <v>90721</v>
       </c>
       <c r="B2650" t="inlineStr">
         <is>
-          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 175N, 30g</t>
+          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 170Q, 30g</t>
         </is>
       </c>
       <c r="C2650" t="inlineStr">
@@ -40231,11 +40231,11 @@
     </row>
     <row r="2651">
       <c r="A2651" t="n">
-        <v>90721</v>
+        <v>87818</v>
       </c>
       <c r="B2651" t="inlineStr">
         <is>
-          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 170Q, 30g</t>
+          <t>MAKE B BATOM EASY MATE WHISPER BEIGE, 3,9g</t>
         </is>
       </c>
       <c r="C2651" t="inlineStr">
@@ -40246,11 +40246,11 @@
     </row>
     <row r="2652">
       <c r="A2652" t="n">
-        <v>87818</v>
+        <v>87820</v>
       </c>
       <c r="B2652" t="inlineStr">
         <is>
-          <t>MAKE B BATOM EASY MATE WHISPER BEIGE, 3,9g</t>
+          <t>MAKE B BATOM EASY MATE WARM CLAY, 3,9g</t>
         </is>
       </c>
       <c r="C2652" t="inlineStr">
@@ -40261,11 +40261,11 @@
     </row>
     <row r="2653">
       <c r="A2653" t="n">
-        <v>87820</v>
+        <v>87787</v>
       </c>
       <c r="B2653" t="inlineStr">
         <is>
-          <t>MAKE B BATOM EASY MATE WARM CLAY, 3,9g</t>
+          <t>MAKE B PLT MULTIF BL/FUS SOFT FUSION 20g</t>
         </is>
       </c>
       <c r="C2653" t="inlineStr">
@@ -40276,41 +40276,41 @@
     </row>
     <row r="2654">
       <c r="A2654" t="n">
-        <v>57753</v>
+        <v>89085</v>
       </c>
       <c r="B2654" t="inlineStr">
         <is>
-          <t>MAKE B ESPONJA MAQ PU</t>
+          <t>NIINA SECRETS GLOSS LABIAL LUMINOUS SUMMER COR 2 12g</t>
         </is>
       </c>
       <c r="C2654" t="inlineStr">
         <is>
-          <t>oBoticário</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
     <row r="2655">
       <c r="A2655" t="n">
-        <v>89568</v>
+        <v>95702</v>
       </c>
       <c r="B2655" t="inlineStr">
         <is>
-          <t>MAKE B MINI MALETA ALL SET</t>
+          <t>COMB NIINA SCRT NEUTRALS NAM/26</t>
         </is>
       </c>
       <c r="C2655" t="inlineStr">
         <is>
-          <t>oBoticário</t>
+          <t>Eudora</t>
         </is>
       </c>
     </row>
     <row r="2656">
       <c r="A2656" t="n">
-        <v>87787</v>
+        <v>90668</v>
       </c>
       <c r="B2656" t="inlineStr">
         <is>
-          <t>MAKE B PLT MULTIF BL/FUS SOFT FUSION 20g</t>
+          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 270Q, 30g</t>
         </is>
       </c>
       <c r="C2656" t="inlineStr">
@@ -40321,56 +40321,56 @@
     </row>
     <row r="2657">
       <c r="A2657" t="n">
-        <v>89085</v>
+        <v>90711</v>
       </c>
       <c r="B2657" t="inlineStr">
         <is>
-          <t>NIINA SECRETS GLOSS LABIAL LUMINOUS SUMMER COR 2 12g</t>
+          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 225N, 30g</t>
         </is>
       </c>
       <c r="C2657" t="inlineStr">
         <is>
-          <t>Eudora</t>
+          <t>oBoticário</t>
         </is>
       </c>
     </row>
     <row r="2658">
       <c r="A2658" t="n">
-        <v>95702</v>
+        <v>90716</v>
       </c>
       <c r="B2658" t="inlineStr">
         <is>
-          <t>COMB NIINA SCRT NEUTRALS NAM/26</t>
+          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 200N, 30g</t>
         </is>
       </c>
       <c r="C2658" t="inlineStr">
         <is>
-          <t>Eudora</t>
+          <t>oBoticário</t>
         </is>
       </c>
     </row>
     <row r="2659">
       <c r="A2659" t="n">
-        <v>56676</v>
+        <v>90719</v>
       </c>
       <c r="B2659" t="inlineStr">
         <is>
-          <t>NIINA REPACK ESPONJA DE MAKE</t>
+          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 180Q, 30g</t>
         </is>
       </c>
       <c r="C2659" t="inlineStr">
         <is>
-          <t>Eudora</t>
+          <t>oBoticário</t>
         </is>
       </c>
     </row>
     <row r="2660">
       <c r="A2660" t="n">
-        <v>90668</v>
+        <v>87819</v>
       </c>
       <c r="B2660" t="inlineStr">
         <is>
-          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 270Q, 30g</t>
+          <t>MAKE B BATOM EASY MATE TRUE PLUM, 3,9g</t>
         </is>
       </c>
       <c r="C2660" t="inlineStr">
@@ -40381,74 +40381,14 @@
     </row>
     <row r="2661">
       <c r="A2661" t="n">
-        <v>90711</v>
+        <v>88819</v>
       </c>
       <c r="B2661" t="inlineStr">
         <is>
-          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 225N, 30g</t>
+          <t>QDB GLOSS SONHOS AVELI 4ml</t>
         </is>
       </c>
       <c r="C2661" t="inlineStr">
-        <is>
-          <t>oBoticário</t>
-        </is>
-      </c>
-    </row>
-    <row r="2662">
-      <c r="A2662" t="n">
-        <v>90716</v>
-      </c>
-      <c r="B2662" t="inlineStr">
-        <is>
-          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 200N, 30g</t>
-        </is>
-      </c>
-      <c r="C2662" t="inlineStr">
-        <is>
-          <t>oBoticário</t>
-        </is>
-      </c>
-    </row>
-    <row r="2663">
-      <c r="A2663" t="n">
-        <v>90719</v>
-      </c>
-      <c r="B2663" t="inlineStr">
-        <is>
-          <t>MAKE B BASE LÍQUIDA MATE SALICYLIC 180Q, 30g</t>
-        </is>
-      </c>
-      <c r="C2663" t="inlineStr">
-        <is>
-          <t>oBoticário</t>
-        </is>
-      </c>
-    </row>
-    <row r="2664">
-      <c r="A2664" t="n">
-        <v>87819</v>
-      </c>
-      <c r="B2664" t="inlineStr">
-        <is>
-          <t>MAKE B BATOM EASY MATE TRUE PLUM, 3,9g</t>
-        </is>
-      </c>
-      <c r="C2664" t="inlineStr">
-        <is>
-          <t>oBoticário</t>
-        </is>
-      </c>
-    </row>
-    <row r="2665">
-      <c r="A2665" t="n">
-        <v>88819</v>
-      </c>
-      <c r="B2665" t="inlineStr">
-        <is>
-          <t>QDB GLOSS SONHOS AVELI 4ml</t>
-        </is>
-      </c>
-      <c r="C2665" t="inlineStr">
         <is>
           <t>Quem Disse Berenice</t>
         </is>

--- a/data/make_iaf.xlsx
+++ b/data/make_iaf.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2661"/>
+  <dimension ref="A1:C2808"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40394,6 +40394,2505 @@
         </is>
       </c>
     </row>
+    <row r="2662">
+      <c r="A2662" t="inlineStr">
+        <is>
+          <t>56276</t>
+        </is>
+      </c>
+      <c r="B2662" t="inlineStr">
+        <is>
+          <t>INTENSE BAT CREM 120 PRM 3,8g</t>
+        </is>
+      </c>
+      <c r="C2662" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2663">
+      <c r="A2663" t="inlineStr">
+        <is>
+          <t>53483</t>
+        </is>
+      </c>
+      <c r="B2663" t="inlineStr">
+        <is>
+          <t>SOPHIE PLT MULTIF DISNEY WISH</t>
+        </is>
+      </c>
+      <c r="C2663" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2664">
+      <c r="A2664" t="inlineStr">
+        <is>
+          <t>49218</t>
+        </is>
+      </c>
+      <c r="B2664" t="inlineStr">
+        <is>
+          <t>MAKE B ESTJ PO COMP HYALURONIC</t>
+        </is>
+      </c>
+      <c r="C2664" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2665">
+      <c r="A2665" t="inlineStr">
+        <is>
+          <t>75921</t>
+        </is>
+      </c>
+      <c r="B2665" t="inlineStr">
+        <is>
+          <t>SOPHIE BATOM ROSA PINK, 3,3g</t>
+        </is>
+      </c>
+      <c r="C2665" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2666">
+      <c r="A2666" t="inlineStr">
+        <is>
+          <t>75920</t>
+        </is>
+      </c>
+      <c r="B2666" t="inlineStr">
+        <is>
+          <t>SOPHIE BATOM LILAS ENCANTO, 3,3g</t>
+        </is>
+      </c>
+      <c r="C2666" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2667">
+      <c r="A2667" t="inlineStr">
+        <is>
+          <t>52193</t>
+        </is>
+      </c>
+      <c r="B2667" t="inlineStr">
+        <is>
+          <t>INTENSE BAT MATE POP 235 V2 3,8g</t>
+        </is>
+      </c>
+      <c r="C2667" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2668">
+      <c r="A2668" t="inlineStr">
+        <is>
+          <t>51595</t>
+        </is>
+      </c>
+      <c r="B2668" t="inlineStr">
+        <is>
+          <t>MAKE B PEDRA VULCANICA ABSORV OL</t>
+        </is>
+      </c>
+      <c r="C2668" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2669">
+      <c r="A2669" t="inlineStr">
+        <is>
+          <t>46373</t>
+        </is>
+      </c>
+      <c r="B2669" t="inlineStr">
+        <is>
+          <t>MAKE B MALET MAQUIAGEM C/ALC PU</t>
+        </is>
+      </c>
+      <c r="C2669" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2670">
+      <c r="A2670" t="inlineStr">
+        <is>
+          <t>57445</t>
+        </is>
+      </c>
+      <c r="B2670" t="inlineStr">
+        <is>
+          <t>MAKE B BAT LIQ VELV/SBLM ONE FREN/ROS 2g</t>
+        </is>
+      </c>
+      <c r="C2670" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2671">
+      <c r="A2671" t="inlineStr">
+        <is>
+          <t>85668</t>
+        </is>
+      </c>
+      <c r="B2671" t="inlineStr">
+        <is>
+          <t>MAKE B ILUM PO COMP FAC ROSE V2 5,4g</t>
+        </is>
+      </c>
+      <c r="C2671" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2672">
+      <c r="A2672" t="inlineStr">
+        <is>
+          <t>58624</t>
+        </is>
+      </c>
+      <c r="B2672" t="inlineStr">
+        <is>
+          <t>MAKE B CORRET LIQ FAC EFFECT 20 V2 5,7ml</t>
+        </is>
+      </c>
+      <c r="C2672" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2673">
+      <c r="A2673" t="inlineStr">
+        <is>
+          <t>85943</t>
+        </is>
+      </c>
+      <c r="B2673" t="inlineStr">
+        <is>
+          <t>MAKE B BAT SHE MULTIF BTY/NAT CHERR 3,6g</t>
+        </is>
+      </c>
+      <c r="C2673" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2674">
+      <c r="A2674" t="inlineStr">
+        <is>
+          <t>53255</t>
+        </is>
+      </c>
+      <c r="B2674" t="inlineStr">
+        <is>
+          <t>MAKE B ESPNJ MAQUIAGEM PU</t>
+        </is>
+      </c>
+      <c r="C2674" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2675">
+      <c r="A2675" t="inlineStr">
+        <is>
+          <t>86954</t>
+        </is>
+      </c>
+      <c r="B2675" t="inlineStr">
+        <is>
+          <t>SOPHIE PLT MULTIF HYDR/LIN SPID/GWEN 17g</t>
+        </is>
+      </c>
+      <c r="C2675" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2676">
+      <c r="A2676" t="inlineStr">
+        <is>
+          <t>83894</t>
+        </is>
+      </c>
+      <c r="B2676" t="inlineStr">
+        <is>
+          <t>MAKE B HID FAC ACQUA JELLY 50g</t>
+        </is>
+      </c>
+      <c r="C2676" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2677">
+      <c r="A2677" t="inlineStr">
+        <is>
+          <t>88012</t>
+        </is>
+      </c>
+      <c r="B2677" t="inlineStr">
+        <is>
+          <t>MAKE B BAT LIQ MAT AC/POL G/BERR V2 5ml</t>
+        </is>
+      </c>
+      <c r="C2677" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2678">
+      <c r="A2678" t="inlineStr">
+        <is>
+          <t>58629</t>
+        </is>
+      </c>
+      <c r="B2678" t="inlineStr">
+        <is>
+          <t>MAKE B CORRET LIQ FAC EFFECT 50 V2 5,7ml</t>
+        </is>
+      </c>
+      <c r="C2678" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2679">
+      <c r="A2679" t="inlineStr">
+        <is>
+          <t>58671</t>
+        </is>
+      </c>
+      <c r="B2679" t="inlineStr">
+        <is>
+          <t>Kit Eudora Niina Secrets - Natal 2024 (2 itens)</t>
+        </is>
+      </c>
+      <c r="C2679" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2680">
+      <c r="A2680" t="inlineStr">
+        <is>
+          <t>57489</t>
+        </is>
+      </c>
+      <c r="B2680" t="inlineStr">
+        <is>
+          <t>NIINA SKIN GEL DE LIMPEZA FACIAL 300g</t>
+        </is>
+      </c>
+      <c r="C2680" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2681">
+      <c r="A2681" t="inlineStr">
+        <is>
+          <t>55437</t>
+        </is>
+      </c>
+      <c r="B2681" t="inlineStr">
+        <is>
+          <t>NIINA SKIN SÉRUM VITAMINA C FACIAL 30ML</t>
+        </is>
+      </c>
+      <c r="C2681" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2682">
+      <c r="A2682" t="inlineStr">
+        <is>
+          <t>7396</t>
+        </is>
+      </c>
+      <c r="B2682" t="inlineStr">
+        <is>
+          <t>NIINA SKIN GEL DE LIMP FAC 100ml</t>
+        </is>
+      </c>
+      <c r="C2682" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2683">
+      <c r="A2683" t="inlineStr">
+        <is>
+          <t>88160</t>
+        </is>
+      </c>
+      <c r="B2683" t="inlineStr">
+        <is>
+          <t>PRESENTE MÃES NIINA SECRETS (3 itens)</t>
+        </is>
+      </c>
+      <c r="C2683" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2684">
+      <c r="A2684" t="inlineStr">
+        <is>
+          <t>55487</t>
+        </is>
+      </c>
+      <c r="B2684" t="inlineStr">
+        <is>
+          <t>NIINA SKIN CREME SORBET PREENCHEDOR 80G</t>
+        </is>
+      </c>
+      <c r="C2684" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2685">
+      <c r="A2685" t="inlineStr">
+        <is>
+          <t>79376</t>
+        </is>
+      </c>
+      <c r="B2685" t="inlineStr">
+        <is>
+          <t>PRESENTE NIINA SECRETS NAMORADOS 2025</t>
+        </is>
+      </c>
+      <c r="C2685" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2686">
+      <c r="A2686" t="inlineStr">
+        <is>
+          <t>7394</t>
+        </is>
+      </c>
+      <c r="B2686" t="inlineStr">
+        <is>
+          <t>NIINA SKIN GEL HID FAC 30ml</t>
+        </is>
+      </c>
+      <c r="C2686" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2687">
+      <c r="A2687" t="inlineStr">
+        <is>
+          <t>55481</t>
+        </is>
+      </c>
+      <c r="B2687" t="inlineStr">
+        <is>
+          <t>NIINA SKIN SÉRUM FACIAL PRÓ COLÁGENO 30ML</t>
+        </is>
+      </c>
+      <c r="C2687" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2688">
+      <c r="A2688" t="inlineStr">
+        <is>
+          <t>87303</t>
+        </is>
+      </c>
+      <c r="B2688" t="inlineStr">
+        <is>
+          <t>NIINA SECRETS ESPELHO POCKET LED</t>
+        </is>
+      </c>
+      <c r="C2688" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2689">
+      <c r="A2689" t="inlineStr">
+        <is>
+          <t>52863</t>
+        </is>
+      </c>
+      <c r="B2689" t="inlineStr">
+        <is>
+          <t>ESTOJO ROTINA ESSENCIAL NIINA SKIN</t>
+        </is>
+      </c>
+      <c r="C2689" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2690">
+      <c r="A2690" t="inlineStr">
+        <is>
+          <t>55438</t>
+        </is>
+      </c>
+      <c r="B2690" t="inlineStr">
+        <is>
+          <t>NIINA SKIN TÔNICO RENOVADOR ANTIOXIDANTE VITAMINA C 110ml</t>
+        </is>
+      </c>
+      <c r="C2690" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2691">
+      <c r="A2691" t="inlineStr">
+        <is>
+          <t>88531</t>
+        </is>
+      </c>
+      <c r="B2691" t="inlineStr">
+        <is>
+          <t>PRESENTE NIINA SECRETS BATOM GLOSS CRYSTAL + BLUSH STICK</t>
+        </is>
+      </c>
+      <c r="C2691" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2692">
+      <c r="A2692" t="inlineStr">
+        <is>
+          <t>51348</t>
+        </is>
+      </c>
+      <c r="B2692" t="inlineStr">
+        <is>
+          <t>NIINA SKIN HIDRATANTE MATIFICANTE ANTIOLEOSIDADE 40g</t>
+        </is>
+      </c>
+      <c r="C2692" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2693">
+      <c r="A2693" t="inlineStr">
+        <is>
+          <t>51781</t>
+        </is>
+      </c>
+      <c r="B2693" t="inlineStr">
+        <is>
+          <t>NIINA SKIN HIDRATANTE REDUTOR DE OLHEIRAS 15g</t>
+        </is>
+      </c>
+      <c r="C2693" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2694">
+      <c r="A2694" t="inlineStr">
+        <is>
+          <t>7290</t>
+        </is>
+      </c>
+      <c r="B2694" t="inlineStr">
+        <is>
+          <t>NIINA SKIN ESF FAC 75g</t>
+        </is>
+      </c>
+      <c r="C2694" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2695">
+      <c r="A2695" t="inlineStr">
+        <is>
+          <t>59189</t>
+        </is>
+      </c>
+      <c r="B2695" t="inlineStr">
+        <is>
+          <t>REFIL NIINA SKIN HIDRATANTE FACIAL 30ml</t>
+        </is>
+      </c>
+      <c r="C2695" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2696">
+      <c r="A2696" t="inlineStr">
+        <is>
+          <t>7379</t>
+        </is>
+      </c>
+      <c r="B2696" t="inlineStr">
+        <is>
+          <t>NIINA SKIN DEMAQ CLEANSING OIL 110ml</t>
+        </is>
+      </c>
+      <c r="C2696" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2697">
+      <c r="A2697" t="inlineStr">
+        <is>
+          <t>89340</t>
+        </is>
+      </c>
+      <c r="B2697" t="inlineStr">
+        <is>
+          <t>PRESENTE KISS ME DEO COL BITOCA + SOUL BATOM MATE VERMELHO</t>
+        </is>
+      </c>
+      <c r="C2697" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2698">
+      <c r="A2698" t="inlineStr">
+        <is>
+          <t>51349</t>
+        </is>
+      </c>
+      <c r="B2698" t="inlineStr">
+        <is>
+          <t>NIINA SKIN MÁSCARA NOTURNA LIP REPAIR 9g</t>
+        </is>
+      </c>
+      <c r="C2698" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2699">
+      <c r="A2699" t="inlineStr">
+        <is>
+          <t>55741</t>
+        </is>
+      </c>
+      <c r="B2699" t="inlineStr">
+        <is>
+          <t>NIINA SECRETS ESPELHO DE MAQUIAGEM</t>
+        </is>
+      </c>
+      <c r="C2699" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2700">
+      <c r="A2700" t="inlineStr">
+        <is>
+          <t>52246</t>
+        </is>
+      </c>
+      <c r="B2700" t="inlineStr">
+        <is>
+          <t>EUDORA NEO DERMO HIDRA MINERAL BALM LABIAL 3,5G</t>
+        </is>
+      </c>
+      <c r="C2700" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2701">
+      <c r="A2701" t="inlineStr">
+        <is>
+          <t>88528</t>
+        </is>
+      </c>
+      <c r="B2701" t="inlineStr">
+        <is>
+          <t>PRESENTE GLAM BLUSH + BATOM LÍQUIDO MATTE TINT</t>
+        </is>
+      </c>
+      <c r="C2701" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2702">
+      <c r="A2702" t="inlineStr">
+        <is>
+          <t>7450</t>
+        </is>
+      </c>
+      <c r="B2702" t="inlineStr">
+        <is>
+          <t>EUDORA NIINA SKIN CREME OVERNIGHT RENOVADOR 45G</t>
+        </is>
+      </c>
+      <c r="C2702" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2703">
+      <c r="A2703" t="inlineStr">
+        <is>
+          <t>56770</t>
+        </is>
+      </c>
+      <c r="B2703" t="inlineStr">
+        <is>
+          <t>EUDORA PORTA BATOM</t>
+        </is>
+      </c>
+      <c r="C2703" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2704">
+      <c r="A2704" t="inlineStr">
+        <is>
+          <t>48132</t>
+        </is>
+      </c>
+      <c r="B2704" t="inlineStr">
+        <is>
+          <t>NIINA SCRT ESPNJ MAQUIAGEM</t>
+        </is>
+      </c>
+      <c r="C2704" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2705">
+      <c r="A2705" t="inlineStr">
+        <is>
+          <t>55441</t>
+        </is>
+      </c>
+      <c r="B2705" t="inlineStr">
+        <is>
+          <t>SACHET NIINA SKIN TONICO RENOVADOR ANTIOXIDANTE VITAMINA C VENDA 2ml</t>
+        </is>
+      </c>
+      <c r="C2705" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2706">
+      <c r="A2706" t="inlineStr">
+        <is>
+          <t>55486</t>
+        </is>
+      </c>
+      <c r="B2706" t="inlineStr">
+        <is>
+          <t>SACHET NIINA SKIN CREME SORBET FIRMADOR VENDA 2G</t>
+        </is>
+      </c>
+      <c r="C2706" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2707">
+      <c r="A2707" t="inlineStr">
+        <is>
+          <t>59696</t>
+        </is>
+      </c>
+      <c r="B2707" t="inlineStr">
+        <is>
+          <t>NIINA SKIN MOUSSE LIMP FAC PINK 150ml</t>
+        </is>
+      </c>
+      <c r="C2707" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2708">
+      <c r="A2708" t="inlineStr">
+        <is>
+          <t>87304</t>
+        </is>
+      </c>
+      <c r="B2708" t="inlineStr">
+        <is>
+          <t>NIINA SECRETS PINC ESP MULTIF PS</t>
+        </is>
+      </c>
+      <c r="C2708" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2709">
+      <c r="A2709" t="inlineStr">
+        <is>
+          <t>90491</t>
+        </is>
+      </c>
+      <c r="B2709" t="inlineStr">
+        <is>
+          <t>COMBO NIINA SKIN MOUSSE+HIDRATANTE BALM</t>
+        </is>
+      </c>
+      <c r="C2709" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2710">
+      <c r="A2710" t="inlineStr">
+        <is>
+          <t>59697</t>
+        </is>
+      </c>
+      <c r="B2710" t="inlineStr">
+        <is>
+          <t>NIINA SKIN HID FAC BALM 15g</t>
+        </is>
+      </c>
+      <c r="C2710" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2711">
+      <c r="A2711" t="inlineStr">
+        <is>
+          <t>56679</t>
+        </is>
+      </c>
+      <c r="B2711" t="inlineStr">
+        <is>
+          <t>NIINA SECRETS MASSAGEADOR FACIAL</t>
+        </is>
+      </c>
+      <c r="C2711" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2712">
+      <c r="A2712" t="inlineStr">
+        <is>
+          <t>85915</t>
+        </is>
+      </c>
+      <c r="B2712" t="inlineStr">
+        <is>
+          <t>NIINA SKIN GEL DE LIMPEZA FACIAL V2 100g</t>
+        </is>
+      </c>
+      <c r="C2712" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2713">
+      <c r="A2713" t="inlineStr">
+        <is>
+          <t>90489</t>
+        </is>
+      </c>
+      <c r="B2713" t="inlineStr">
+        <is>
+          <t>COMBO NIINA CLEANSING OIL + BRUMA</t>
+        </is>
+      </c>
+      <c r="C2713" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2714">
+      <c r="A2714" t="inlineStr">
+        <is>
+          <t>59225</t>
+        </is>
+      </c>
+      <c r="B2714" t="inlineStr">
+        <is>
+          <t>NIINA SCRT CLDA / BNH 100ml</t>
+        </is>
+      </c>
+      <c r="C2714" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2715">
+      <c r="A2715" t="inlineStr">
+        <is>
+          <t>90850</t>
+        </is>
+      </c>
+      <c r="B2715" t="inlineStr">
+        <is>
+          <t>PRESENTE NIINA SKIN ESFOLIANTE ENZIMÁTICO</t>
+        </is>
+      </c>
+      <c r="C2715" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2716">
+      <c r="A2716" t="inlineStr">
+        <is>
+          <t>90420</t>
+        </is>
+      </c>
+      <c r="B2716" t="inlineStr">
+        <is>
+          <t>Presente Niina (2 Itens)</t>
+        </is>
+      </c>
+      <c r="C2716" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2717">
+      <c r="A2717" t="inlineStr">
+        <is>
+          <t>85845</t>
+        </is>
+      </c>
+      <c r="B2717" t="inlineStr">
+        <is>
+          <t>NIINA SKIN GEL LIMPEZA FACIAL V2 300g</t>
+        </is>
+      </c>
+      <c r="C2717" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2718">
+      <c r="A2718" t="inlineStr">
+        <is>
+          <t>90433</t>
+        </is>
+      </c>
+      <c r="B2718" t="inlineStr">
+        <is>
+          <t>Presente Niina Palette (1 Item)</t>
+        </is>
+      </c>
+      <c r="C2718" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" t="inlineStr">
+        <is>
+          <t>96270</t>
+        </is>
+      </c>
+      <c r="B2719" t="inlineStr">
+        <is>
+          <t>COMBO NIINA SECRETS BATOM LÍQUIDO SKINNY MATTE VERM HIBISCO + BATOM DUO PERFECT MATCH AVELÃ</t>
+        </is>
+      </c>
+      <c r="C2719" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="A2720" t="inlineStr">
+        <is>
+          <t>86804</t>
+        </is>
+      </c>
+      <c r="B2720" t="inlineStr">
+        <is>
+          <t>NIINA SKIN CREM SORB FACIAL FIRM V2 80g</t>
+        </is>
+      </c>
+      <c r="C2720" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" t="inlineStr">
+        <is>
+          <t>90414</t>
+        </is>
+      </c>
+      <c r="B2721" t="inlineStr">
+        <is>
+          <t>Presente Niina Skin (2 itens)</t>
+        </is>
+      </c>
+      <c r="C2721" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" t="inlineStr">
+        <is>
+          <t>55484</t>
+        </is>
+      </c>
+      <c r="B2722" t="inlineStr">
+        <is>
+          <t>SACHET NIINA SKIN SÉRUM FIRMADOR LIFTING VENDA 2ML</t>
+        </is>
+      </c>
+      <c r="C2722" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" t="inlineStr">
+        <is>
+          <t>89082</t>
+        </is>
+      </c>
+      <c r="B2723" t="inlineStr">
+        <is>
+          <t>NIINA SECRETS PALETTE MULTIFUNCIONAL LUMINOUS SUMMER COR 2 7g</t>
+        </is>
+      </c>
+      <c r="C2723" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2724">
+      <c r="A2724" t="inlineStr">
+        <is>
+          <t>82102</t>
+        </is>
+      </c>
+      <c r="B2724" t="inlineStr">
+        <is>
+          <t>BATOM ROUGE À LÈVRES, 3,5 g</t>
+        </is>
+      </c>
+      <c r="C2724" t="inlineStr">
+        <is>
+          <t>O.U.I</t>
+        </is>
+      </c>
+    </row>
+    <row r="2725">
+      <c r="A2725" t="inlineStr">
+        <is>
+          <t>75331</t>
+        </is>
+      </c>
+      <c r="B2725" t="inlineStr">
+        <is>
+          <t>QDB GLOSS LAB SUPERBRILHO ROSEX 4ml</t>
+        </is>
+      </c>
+      <c r="C2725" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" t="inlineStr">
+        <is>
+          <t>50535</t>
+        </is>
+      </c>
+      <c r="B2726" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ ACORDEI ASSIM 02 Q 30ml</t>
+        </is>
+      </c>
+      <c r="C2726" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" t="inlineStr">
+        <is>
+          <t>50527</t>
+        </is>
+      </c>
+      <c r="B2727" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ ACORDEI ASSIM 04 Q 30ml</t>
+        </is>
+      </c>
+      <c r="C2727" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" t="inlineStr">
+        <is>
+          <t>50526</t>
+        </is>
+      </c>
+      <c r="B2728" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ ACORDEI ASSIM 06 Q 30ml</t>
+        </is>
+      </c>
+      <c r="C2728" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" t="inlineStr">
+        <is>
+          <t>77552</t>
+        </is>
+      </c>
+      <c r="B2729" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ SUPERMAT COR 04 F 30ml RPCK</t>
+        </is>
+      </c>
+      <c r="C2729" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2730">
+      <c r="A2730" t="inlineStr">
+        <is>
+          <t>77553</t>
+        </is>
+      </c>
+      <c r="B2730" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ SUPERMAT COR 04 Q 30ml RPCK</t>
+        </is>
+      </c>
+      <c r="C2730" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2731">
+      <c r="A2731" t="inlineStr">
+        <is>
+          <t>54749</t>
+        </is>
+      </c>
+      <c r="B2731" t="inlineStr">
+        <is>
+          <t>QDB LAP BAT 3/1 FABER CASTEL DAMASC 1,2g</t>
+        </is>
+      </c>
+      <c r="C2731" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" t="inlineStr">
+        <is>
+          <t>52870</t>
+        </is>
+      </c>
+      <c r="B2732" t="inlineStr">
+        <is>
+          <t>QDB DIVERTIDA MAKE PLT MULTIF 1 12g</t>
+        </is>
+      </c>
+      <c r="C2732" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2733">
+      <c r="A2733" t="inlineStr">
+        <is>
+          <t>75330</t>
+        </is>
+      </c>
+      <c r="B2733" t="inlineStr">
+        <is>
+          <t>QDB GLOSS LAB SUPERBRILHO ROSADEX 4ml</t>
+        </is>
+      </c>
+      <c r="C2733" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2734">
+      <c r="A2734" t="inlineStr">
+        <is>
+          <t>84485</t>
+        </is>
+      </c>
+      <c r="B2734" t="inlineStr">
+        <is>
+          <t>QDB BAT LIQ SUPERMAT BEIJO QUE FICA 4ml</t>
+        </is>
+      </c>
+      <c r="C2734" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2735">
+      <c r="A2735" t="inlineStr">
+        <is>
+          <t>75292</t>
+        </is>
+      </c>
+      <c r="B2735" t="inlineStr">
+        <is>
+          <t>QDB BATOM HIDRATANTE ROSARAO RPCK 3,8g</t>
+        </is>
+      </c>
+      <c r="C2735" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" t="inlineStr">
+        <is>
+          <t>27251</t>
+        </is>
+      </c>
+      <c r="B2736" t="inlineStr">
+        <is>
+          <t>QDB LAPIS OLHOS PRETUCO 1,2G</t>
+        </is>
+      </c>
+      <c r="C2736" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" t="inlineStr">
+        <is>
+          <t>54748</t>
+        </is>
+      </c>
+      <c r="B2737" t="inlineStr">
+        <is>
+          <t>QDB LAP BAT 3/1 FABER CASTELL VERM 1,2g</t>
+        </is>
+      </c>
+      <c r="C2737" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" t="inlineStr">
+        <is>
+          <t>75231</t>
+        </is>
+      </c>
+      <c r="B2738" t="inlineStr">
+        <is>
+          <t>QUEM DISSE BERENICE BATOM LÍQUIDO SUPERMATE CACAULI 4ML</t>
+        </is>
+      </c>
+      <c r="C2738" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" t="inlineStr">
+        <is>
+          <t>75220</t>
+        </is>
+      </c>
+      <c r="B2739" t="inlineStr">
+        <is>
+          <t>QDB BAT LIQ SUPERMATE VINHELI 4ml</t>
+        </is>
+      </c>
+      <c r="C2739" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2740">
+      <c r="A2740" t="inlineStr">
+        <is>
+          <t>75230</t>
+        </is>
+      </c>
+      <c r="B2740" t="inlineStr">
+        <is>
+          <t>QUEM DISSE BERENICE BATOM LÍQUIDO SUPERMATE ROSEIRALI 4ML</t>
+        </is>
+      </c>
+      <c r="C2740" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2741">
+      <c r="A2741" t="inlineStr">
+        <is>
+          <t>75232</t>
+        </is>
+      </c>
+      <c r="B2741" t="inlineStr">
+        <is>
+          <t>QDB BAT LIQ SUPERMATE AMORLI 4ml</t>
+        </is>
+      </c>
+      <c r="C2741" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2742">
+      <c r="A2742" t="inlineStr">
+        <is>
+          <t>75236</t>
+        </is>
+      </c>
+      <c r="B2742" t="inlineStr">
+        <is>
+          <t>QDB BAT LIQ SUPERMATE ROSALI 4ml</t>
+        </is>
+      </c>
+      <c r="C2742" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" t="inlineStr">
+        <is>
+          <t>75308</t>
+        </is>
+      </c>
+      <c r="B2743" t="inlineStr">
+        <is>
+          <t>QDB BATOM MATE ALTA PIGMENTACAO BORDONITO RPCK 3,8g</t>
+        </is>
+      </c>
+      <c r="C2743" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" t="inlineStr">
+        <is>
+          <t>59760</t>
+        </is>
+      </c>
+      <c r="B2744" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ LEV TUDO COR 07N V2 30ml</t>
+        </is>
+      </c>
+      <c r="C2744" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="inlineStr">
+        <is>
+          <t>75221</t>
+        </is>
+      </c>
+      <c r="B2745" t="inlineStr">
+        <is>
+          <t>QUEM DISSE BERENICE BATOM LÍQUIDO SUPERMATE MARSALILI 4ML</t>
+        </is>
+      </c>
+      <c r="C2745" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="inlineStr">
+        <is>
+          <t>75223</t>
+        </is>
+      </c>
+      <c r="B2746" t="inlineStr">
+        <is>
+          <t>QDB BAT LIQ SUPERMATE MARRONLI 4ml</t>
+        </is>
+      </c>
+      <c r="C2746" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="inlineStr">
+        <is>
+          <t>75226</t>
+        </is>
+      </c>
+      <c r="B2747" t="inlineStr">
+        <is>
+          <t>QDB BAT LIQ SUPERMATE MORENALI 4ml</t>
+        </is>
+      </c>
+      <c r="C2747" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="inlineStr">
+        <is>
+          <t>75303</t>
+        </is>
+      </c>
+      <c r="B2748" t="inlineStr">
+        <is>
+          <t>QDB BAT MAT ALT PIGM VERMEREJA 3,8g RPCK</t>
+        </is>
+      </c>
+      <c r="C2748" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="inlineStr">
+        <is>
+          <t>72701</t>
+        </is>
+      </c>
+      <c r="B2749" t="inlineStr">
+        <is>
+          <t>QDB BATOM VOLUMAO ROSEIRE 3,4g</t>
+        </is>
+      </c>
+      <c r="C2749" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="inlineStr">
+        <is>
+          <t>85925</t>
+        </is>
+      </c>
+      <c r="B2750" t="inlineStr">
+        <is>
+          <t>QDB PLT MULTIF DOSE DE COR 12g</t>
+        </is>
+      </c>
+      <c r="C2750" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="inlineStr">
+        <is>
+          <t>86133</t>
+        </is>
+      </c>
+      <c r="B2751" t="inlineStr">
+        <is>
+          <t>QDB BAT CREM POP ROSA RADIANTE 3,6g</t>
+        </is>
+      </c>
+      <c r="C2751" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="inlineStr">
+        <is>
+          <t>86132</t>
+        </is>
+      </c>
+      <c r="B2752" t="inlineStr">
+        <is>
+          <t>QDB BAT CREM POP ROSA MALVA 3,6g</t>
+        </is>
+      </c>
+      <c r="C2752" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="inlineStr">
+        <is>
+          <t>87887</t>
+        </is>
+      </c>
+      <c r="B2753" t="inlineStr">
+        <is>
+          <t>QDB JELLY TINT BLUSH BORDO FRESH 5g</t>
+        </is>
+      </c>
+      <c r="C2753" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="inlineStr">
+        <is>
+          <t>86134</t>
+        </is>
+      </c>
+      <c r="B2754" t="inlineStr">
+        <is>
+          <t>QDB BAT CREM POP NUDE AVELA 3,6g</t>
+        </is>
+      </c>
+      <c r="C2754" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2755">
+      <c r="A2755" t="inlineStr">
+        <is>
+          <t>86137</t>
+        </is>
+      </c>
+      <c r="B2755" t="inlineStr">
+        <is>
+          <t>QDB BAT SEMIMATE POP VERM/ICONICO 3,6g</t>
+        </is>
+      </c>
+      <c r="C2755" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2756">
+      <c r="A2756" t="inlineStr">
+        <is>
+          <t>59358</t>
+        </is>
+      </c>
+      <c r="B2756" t="inlineStr">
+        <is>
+          <t>QDB LAP OLHOS PRETITO 1,1g</t>
+        </is>
+      </c>
+      <c r="C2756" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2757">
+      <c r="A2757" t="inlineStr">
+        <is>
+          <t>87886</t>
+        </is>
+      </c>
+      <c r="B2757" t="inlineStr">
+        <is>
+          <t>QDB JELLY TINT BLUSH PINK FRESH 5g</t>
+        </is>
+      </c>
+      <c r="C2757" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2758">
+      <c r="A2758" t="inlineStr">
+        <is>
+          <t>50533</t>
+        </is>
+      </c>
+      <c r="B2758" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ ACORDEI ASSIM 10 N 30ml</t>
+        </is>
+      </c>
+      <c r="C2758" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2759">
+      <c r="A2759" t="inlineStr">
+        <is>
+          <t>86135</t>
+        </is>
+      </c>
+      <c r="B2759" t="inlineStr">
+        <is>
+          <t>QDB BAT SEMIMATE POP MARR/GLACE 3,6g</t>
+        </is>
+      </c>
+      <c r="C2759" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2760">
+      <c r="A2760" t="inlineStr">
+        <is>
+          <t>59359</t>
+        </is>
+      </c>
+      <c r="B2760" t="inlineStr">
+        <is>
+          <t>QDB LAP OLHOS MARRONTITO 1,1g</t>
+        </is>
+      </c>
+      <c r="C2760" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2761">
+      <c r="A2761" t="inlineStr">
+        <is>
+          <t>86136</t>
+        </is>
+      </c>
+      <c r="B2761" t="inlineStr">
+        <is>
+          <t>QDB BAT SEMIMATE POP ROS/SUPREMO 3,6g</t>
+        </is>
+      </c>
+      <c r="C2761" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2762">
+      <c r="A2762" t="inlineStr">
+        <is>
+          <t>77557</t>
+        </is>
+      </c>
+      <c r="B2762" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ SUPERMAT COR 06 Q 30ml RPCK</t>
+        </is>
+      </c>
+      <c r="C2762" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2763">
+      <c r="A2763" t="inlineStr">
+        <is>
+          <t>75245</t>
+        </is>
+      </c>
+      <c r="B2763" t="inlineStr">
+        <is>
+          <t>QDB BAT LIQ SUPERMATE TINTOLI 4ml</t>
+        </is>
+      </c>
+      <c r="C2763" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2764">
+      <c r="A2764" t="inlineStr">
+        <is>
+          <t>86126</t>
+        </is>
+      </c>
+      <c r="B2764" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ POP 210Q 30ml</t>
+        </is>
+      </c>
+      <c r="C2764" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2765">
+      <c r="A2765" t="inlineStr">
+        <is>
+          <t>86125</t>
+        </is>
+      </c>
+      <c r="B2765" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ POP 200N 30ml</t>
+        </is>
+      </c>
+      <c r="C2765" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2766">
+      <c r="A2766" t="inlineStr">
+        <is>
+          <t>86123</t>
+        </is>
+      </c>
+      <c r="B2766" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQUIDA POP 150Q 30ml</t>
+        </is>
+      </c>
+      <c r="C2766" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2767">
+      <c r="A2767" t="inlineStr">
+        <is>
+          <t>86128</t>
+        </is>
+      </c>
+      <c r="B2767" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ POP 240F 30ml</t>
+        </is>
+      </c>
+      <c r="C2767" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2768">
+      <c r="A2768" t="inlineStr">
+        <is>
+          <t>86120</t>
+        </is>
+      </c>
+      <c r="B2768" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ POP 100F 30ml</t>
+        </is>
+      </c>
+      <c r="C2768" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2769">
+      <c r="A2769" t="inlineStr">
+        <is>
+          <t>89483</t>
+        </is>
+      </c>
+      <c r="B2769" t="inlineStr">
+        <is>
+          <t>NIINA SECRETS PALETTE MULTIFUNCIONAL LUMINOUS SUMMER COR 3 7g</t>
+        </is>
+      </c>
+      <c r="C2769" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2770">
+      <c r="A2770" t="inlineStr">
+        <is>
+          <t>85846</t>
+        </is>
+      </c>
+      <c r="B2770" t="inlineStr">
+        <is>
+          <t>MAKE B BAS LIQ C/GLYCOL TX 130 V2 30g</t>
+        </is>
+      </c>
+      <c r="C2770" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2771">
+      <c r="A2771" t="inlineStr">
+        <is>
+          <t>85856</t>
+        </is>
+      </c>
+      <c r="B2771" t="inlineStr">
+        <is>
+          <t>MAKE B BAS LIQ C/GLYCOL TX 220 V2 30g</t>
+        </is>
+      </c>
+      <c r="C2771" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2772">
+      <c r="A2772" t="inlineStr">
+        <is>
+          <t>70313</t>
+        </is>
+      </c>
+      <c r="B2772" t="inlineStr">
+        <is>
+          <t>QDB PO ILUMINADOR COMPACTO ROSELUZ 5g</t>
+        </is>
+      </c>
+      <c r="C2772" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2773">
+      <c r="A2773" t="inlineStr">
+        <is>
+          <t>58626</t>
+        </is>
+      </c>
+      <c r="B2773" t="inlineStr">
+        <is>
+          <t>MAKE B CORRET LIQ FAC EFFECT 25 V2 5,7ml</t>
+        </is>
+      </c>
+      <c r="C2773" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2774">
+      <c r="A2774" t="inlineStr">
+        <is>
+          <t>88015</t>
+        </is>
+      </c>
+      <c r="B2774" t="inlineStr">
+        <is>
+          <t>MAKE B BAT LIQ MAT AC/POL DEEP/RO V2 5ml</t>
+        </is>
+      </c>
+      <c r="C2774" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2775">
+      <c r="A2775" t="inlineStr">
+        <is>
+          <t>73533</t>
+        </is>
+      </c>
+      <c r="B2775" t="inlineStr">
+        <is>
+          <t>MAKE B CREM REDUT BOLSA OLH SKIN 15ml V2</t>
+        </is>
+      </c>
+      <c r="C2775" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2776">
+      <c r="A2776" t="inlineStr">
+        <is>
+          <t>82424</t>
+        </is>
+      </c>
+      <c r="B2776" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ ALTA COBERT COR 06N 30ml</t>
+        </is>
+      </c>
+      <c r="C2776" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2777">
+      <c r="A2777" t="inlineStr">
+        <is>
+          <t>82416</t>
+        </is>
+      </c>
+      <c r="B2777" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ ALTA COBERT COR 02Q 30ml</t>
+        </is>
+      </c>
+      <c r="C2777" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2778">
+      <c r="A2778" t="inlineStr">
+        <is>
+          <t>82423</t>
+        </is>
+      </c>
+      <c r="B2778" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ ALTA COBERT COR 05Q 30ml</t>
+        </is>
+      </c>
+      <c r="C2778" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2779">
+      <c r="A2779" t="inlineStr">
+        <is>
+          <t>82427</t>
+        </is>
+      </c>
+      <c r="B2779" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ ALTA COBERT COR 07Q 30ml</t>
+        </is>
+      </c>
+      <c r="C2779" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2780">
+      <c r="A2780" t="inlineStr">
+        <is>
+          <t>82429</t>
+        </is>
+      </c>
+      <c r="B2780" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ ALTA COBERT COR 09Q 30ml</t>
+        </is>
+      </c>
+      <c r="C2780" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2781">
+      <c r="A2781" t="inlineStr">
+        <is>
+          <t>82422</t>
+        </is>
+      </c>
+      <c r="B2781" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ ALTA COBERT COR 04N 30ml</t>
+        </is>
+      </c>
+      <c r="C2781" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2782">
+      <c r="A2782" t="inlineStr">
+        <is>
+          <t>79495</t>
+        </is>
+      </c>
+      <c r="B2782" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ SUPERMAT COR 11 N 30ml RPCK</t>
+        </is>
+      </c>
+      <c r="C2782" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2783">
+      <c r="A2783" t="inlineStr">
+        <is>
+          <t>83895</t>
+        </is>
+      </c>
+      <c r="B2783" t="inlineStr">
+        <is>
+          <t>MAKE B BRUMA NOT BTY SLEEP WT SKIN 100ml</t>
+        </is>
+      </c>
+      <c r="C2783" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2784">
+      <c r="A2784" t="inlineStr">
+        <is>
+          <t>86728</t>
+        </is>
+      </c>
+      <c r="B2784" t="inlineStr">
+        <is>
+          <t>COMBO NIINA SCRT 02 NAT/24</t>
+        </is>
+      </c>
+      <c r="C2784" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2785">
+      <c r="A2785" t="inlineStr">
+        <is>
+          <t>44580</t>
+        </is>
+      </c>
+      <c r="B2785" t="inlineStr">
+        <is>
+          <t>MAKE B PINC ESPIRAL P/PELE</t>
+        </is>
+      </c>
+      <c r="C2785" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2786">
+      <c r="A2786" t="inlineStr">
+        <is>
+          <t>82433</t>
+        </is>
+      </c>
+      <c r="B2786" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ ALTA COBERT COR 12Q 30ml</t>
+        </is>
+      </c>
+      <c r="C2786" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2787">
+      <c r="A2787" t="inlineStr">
+        <is>
+          <t>82435</t>
+        </is>
+      </c>
+      <c r="B2787" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ ALTA COBERT COR 14Q 30ml</t>
+        </is>
+      </c>
+      <c r="C2787" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2788">
+      <c r="A2788" t="inlineStr">
+        <is>
+          <t>82415</t>
+        </is>
+      </c>
+      <c r="B2788" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ ALTA COBERT COR 01N 30ml</t>
+        </is>
+      </c>
+      <c r="C2788" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2789">
+      <c r="A2789" t="inlineStr">
+        <is>
+          <t>82425</t>
+        </is>
+      </c>
+      <c r="B2789" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ ALTA COBERT COR 06Q 30ml</t>
+        </is>
+      </c>
+      <c r="C2789" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2790">
+      <c r="A2790" t="inlineStr">
+        <is>
+          <t>82420</t>
+        </is>
+      </c>
+      <c r="B2790" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ ALTA COBERT COR 04F 30ml</t>
+        </is>
+      </c>
+      <c r="C2790" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2791">
+      <c r="A2791" t="inlineStr">
+        <is>
+          <t>82431</t>
+        </is>
+      </c>
+      <c r="B2791" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ ALTA COBERT COR 10N 30ml</t>
+        </is>
+      </c>
+      <c r="C2791" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2792">
+      <c r="A2792" t="inlineStr">
+        <is>
+          <t>82439</t>
+        </is>
+      </c>
+      <c r="B2792" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ ALTA COBERT COR 01F 30ml</t>
+        </is>
+      </c>
+      <c r="C2792" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2793">
+      <c r="A2793" t="inlineStr">
+        <is>
+          <t>54750</t>
+        </is>
+      </c>
+      <c r="B2793" t="inlineStr">
+        <is>
+          <t>QDB LAP BAT 3/1 FABER CASTELL ROSA 1,2g</t>
+        </is>
+      </c>
+      <c r="C2793" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2794">
+      <c r="A2794" t="inlineStr">
+        <is>
+          <t>94875</t>
+        </is>
+      </c>
+      <c r="B2794" t="inlineStr">
+        <is>
+          <t>MAKE B PRIMER FAC DRPS OF BEAUTY V2 30ml</t>
+        </is>
+      </c>
+      <c r="C2794" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2795">
+      <c r="A2795" t="inlineStr">
+        <is>
+          <t>88011</t>
+        </is>
+      </c>
+      <c r="B2795" t="inlineStr">
+        <is>
+          <t>MAKE B BAT LIQ MAT AC/POL EXO/ROS V2 5ml</t>
+        </is>
+      </c>
+      <c r="C2795" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2796">
+      <c r="A2796" t="inlineStr">
+        <is>
+          <t>56765</t>
+        </is>
+      </c>
+      <c r="B2796" t="inlineStr">
+        <is>
+          <t>NIINA SECRETS HAIR CLIP</t>
+        </is>
+      </c>
+      <c r="C2796" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2797">
+      <c r="A2797" t="inlineStr">
+        <is>
+          <t>85848</t>
+        </is>
+      </c>
+      <c r="B2797" t="inlineStr">
+        <is>
+          <t>MAKE B BAS LIQ C/GLYCOL TX 190 V2 30g</t>
+        </is>
+      </c>
+      <c r="C2797" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+    </row>
+    <row r="2798">
+      <c r="A2798" t="inlineStr">
+        <is>
+          <t>75329</t>
+        </is>
+      </c>
+      <c r="B2798" t="inlineStr">
+        <is>
+          <t>QDB GLOSS LAB SUPERBRILHO MALVALEX 4ml</t>
+        </is>
+      </c>
+      <c r="C2798" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2799">
+      <c r="A2799" t="inlineStr">
+        <is>
+          <t>55154</t>
+        </is>
+      </c>
+      <c r="B2799" t="inlineStr">
+        <is>
+          <t>CJ FLAC NIINA SCRT BLOOM 1x</t>
+        </is>
+      </c>
+      <c r="C2799" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2800">
+      <c r="A2800" t="inlineStr">
+        <is>
+          <t>90341</t>
+        </is>
+      </c>
+      <c r="B2800" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ INSTAMATTE 130Q V2 30ml</t>
+        </is>
+      </c>
+      <c r="C2800" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2801">
+      <c r="A2801" t="inlineStr">
+        <is>
+          <t>90345</t>
+        </is>
+      </c>
+      <c r="B2801" t="inlineStr">
+        <is>
+          <t>QDB BASE LIQ INSTAMATTE 175Q 30ml</t>
+        </is>
+      </c>
+      <c r="C2801" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2802">
+      <c r="A2802" t="inlineStr">
+        <is>
+          <t>94188</t>
+        </is>
+      </c>
+      <c r="B2802" t="inlineStr">
+        <is>
+          <t>QDB BLUSH STCK NAH/CARD CHARMING 5g</t>
+        </is>
+      </c>
+      <c r="C2802" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2803">
+      <c r="A2803" t="inlineStr">
+        <is>
+          <t>94189</t>
+        </is>
+      </c>
+      <c r="B2803" t="inlineStr">
+        <is>
+          <t>QDB BLUSH STCK NAH/CARD LOVELY 5g</t>
+        </is>
+      </c>
+      <c r="C2803" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2804">
+      <c r="A2804" t="inlineStr">
+        <is>
+          <t>90115</t>
+        </is>
+      </c>
+      <c r="B2804" t="inlineStr">
+        <is>
+          <t>QDB LAP BAT NAH/CARD BOLD 1,1g</t>
+        </is>
+      </c>
+      <c r="C2804" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2805">
+      <c r="A2805" t="inlineStr">
+        <is>
+          <t>90116</t>
+        </is>
+      </c>
+      <c r="B2805" t="inlineStr">
+        <is>
+          <t>QDB LAP BAT NAH/CARD BRAVE 1,1g</t>
+        </is>
+      </c>
+      <c r="C2805" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2806">
+      <c r="A2806" t="inlineStr">
+        <is>
+          <t>89368</t>
+        </is>
+      </c>
+      <c r="B2806" t="inlineStr">
+        <is>
+          <t>QDB LIP OIL FEIRA MORANGO 3,5ml</t>
+        </is>
+      </c>
+      <c r="C2806" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2807">
+      <c r="A2807" t="inlineStr">
+        <is>
+          <t>89369</t>
+        </is>
+      </c>
+      <c r="B2807" t="inlineStr">
+        <is>
+          <t>QDB LIP OIL FEIRA PESSEGO 3,5ml</t>
+        </is>
+      </c>
+      <c r="C2807" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2808">
+      <c r="A2808" t="inlineStr">
+        <is>
+          <t>89370</t>
+        </is>
+      </c>
+      <c r="B2808" t="inlineStr">
+        <is>
+          <t>QDB LIP OIL FEIRA TANGERINA 3,5ml</t>
+        </is>
+      </c>
+      <c r="C2808" t="inlineStr">
+        <is>
+          <t>Quem Disse Berenice</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
